--- a/artfynd/A 55788-2025 artfynd.xlsx
+++ b/artfynd/A 55788-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118070005</v>
+        <v>113678237</v>
       </c>
       <c r="B2" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+          <t>Svartkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664125</v>
+        <v>664202</v>
       </c>
       <c r="R2" t="n">
-        <v>6640963</v>
+        <v>6641046</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,31 +756,35 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118070095</v>
+        <v>115366499</v>
       </c>
       <c r="B3" t="n">
-        <v>57443</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,42 +792,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+          <t>NV om Ältsjön, ca 1,45 km VNV Länna station, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664098</v>
+        <v>664201</v>
       </c>
       <c r="R3" t="n">
-        <v>6641283</v>
+        <v>6641048</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +849,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I barksprickor på grov gammal ek (omkrets vid brösthöjd 311 cm).</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,55 +878,51 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118069426</v>
+        <v>118069531</v>
       </c>
       <c r="B4" t="n">
-        <v>104853</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>664064</v>
+        <v>664206</v>
       </c>
       <c r="R4" t="n">
-        <v>6640988</v>
+        <v>6641051</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,37 +994,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118069434</v>
+        <v>118069616</v>
       </c>
       <c r="B5" t="n">
-        <v>104853</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221141</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663984</v>
+        <v>664181</v>
       </c>
       <c r="R5" t="n">
-        <v>6640995</v>
+        <v>6641087</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1065,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118070006</v>
+        <v>118069983</v>
       </c>
       <c r="B6" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,31 +1102,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1146,13 +1131,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>664089</v>
+        <v>664139</v>
       </c>
       <c r="R6" t="n">
-        <v>6641047</v>
+        <v>6641331</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,12 +1161,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,6 +1190,1105 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118069977</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>664052</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6640960</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118070005</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>664125</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6640963</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118070006</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>664089</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6641047</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118070095</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>664098</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6641283</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118069426</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>664064</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6640988</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118069434</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>663984</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6640995</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118069529</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>663895</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6641072</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118069530</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>664204</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6641045</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118069440</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>664071</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6640952</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118069439</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>664079</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6640945</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118069617</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>664173</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6641096</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
